--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/loginUserSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/loginUserSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
-  <si>
-    <t>Statement: loginUserSchema – validate login credentials. Fields: email, password.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="107">
+  <si>
+    <t>Statement: loginUserSchema – Validates login credentials using Zod safeParse. Returns { success: true, data } when both fields satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field on any violation. Required fields: email (valid email format; surrounding whitespace is trimmed), password (8–64 characters with at least one uppercase letter, one digit, and one special character; must not be empty).</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>email format | len(password) ≥ 1</t>
+    <t>Input is passed directly to loginUserSchema.safeParse(). email rules: valid format, surrounding whitespace trimmed. password rules: 8–64 characters, at least one uppercase letter, one digit, one special character, must not be empty.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: LoginUserInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match schema.</t>
+    <t>On success: parsed data matches the (trimmed) input. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,46 +64,58 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>All fields valid</t>
-  </si>
-  <si>
-    <t>Email + Password correct</t>
-  </si>
-  <si>
-    <t>Email presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>Password presence</t>
-  </si>
-  <si>
-    <t>Password value</t>
-  </si>
-  <si>
-    <t>Non-empty</t>
-  </si>
-  <si>
-    <t>Empty string</t>
-  </si>
-  <si>
-    <t>Email format</t>
-  </si>
-  <si>
-    <t>Valid RFC</t>
-  </si>
-  <si>
-    <t>Invalid format</t>
-  </si>
-  <si>
-    <t>Email whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace (trimmed)</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>Both email and password valid → success: true, parsed data equals input</t>
+  </si>
+  <si>
+    <t>email presence</t>
+  </si>
+  <si>
+    <t>email omitted → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>password presence</t>
+  </si>
+  <si>
+    <t>password omitted → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password value</t>
+  </si>
+  <si>
+    <t>password: "" (empty string) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>email format</t>
+  </si>
+  <si>
+    <t>email: "invalidemail.com" (missing @) → success: false, error path contains "email"</t>
+  </si>
+  <si>
+    <t>email whitespace</t>
+  </si>
+  <si>
+    <t>email: "  admin@gymtrackerpro.com  " (surrounding whitespace) → success: true, parsed email is "admin@gymtrackerpro.com"</t>
+  </si>
+  <si>
+    <t>password uppercase</t>
+  </si>
+  <si>
+    <t>password: "validpassword1!" (no uppercase letter) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password digit</t>
+  </si>
+  <si>
+    <t>password: "ValidPassword!" (no digit) → success: false, error path contains "password"</t>
+  </si>
+  <si>
+    <t>password special char</t>
+  </si>
+  <si>
+    <t>password: "ValidPassword1" (no special character) → success: false, error path contains "password"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -124,10 +136,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid credentials</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>both email and password provided with valid values</t>
+  </si>
+  <si>
+    <t>success: true, parsed data equals input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -136,34 +148,58 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Missing email</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>valid login data with email field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "email"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Missing password</t>
+    <t>valid login data with password field omitted</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "password"</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Empty password</t>
+    <t>valid login data with password: "" (empty string)</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Email="invalidemail.com"</t>
+    <t>valid login data with email: "invalidemail.com" (missing @)</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>email="  admin@gymtrackerpro.com  " (padded)</t>
+    <t>valid login data with email: "  admin@gymtrackerpro.com  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed email is "admin@gymtrackerpro.com"</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>valid login data with password: "validpassword1!" (no uppercase letter)</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>valid login data with password: "ValidPassword!" (no digit)</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>valid login data with password: "ValidPassword1" (no special character)</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -172,37 +208,67 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Password length</t>
-  </si>
-  <si>
-    <t>0 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>1 char (At Min)</t>
-  </si>
-  <si>
-    <t>2 chars (Above Min)</t>
+    <t>password length</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(4) (length 7, min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(5) (length 8, min): at minimum → success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(6) (length 9, min + 1): above minimum → success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(60) (length 63, max - 1): below maximum → success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(61) (length 64, max): at maximum → success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>password: "P1@" + "a".repeat(62) (length 65, max + 1): above maximum → success: false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Pass len 0</t>
-  </si>
-  <si>
-    <t>password len 0</t>
-  </si>
-  <si>
-    <t>BVA-1 Pass len 1</t>
-  </si>
-  <si>
-    <t>password len 1</t>
-  </si>
-  <si>
-    <t>BVA-1 Pass len 2</t>
-  </si>
-  <si>
-    <t>password len 2</t>
+    <t>BVA-1 (pwd=7)</t>
+  </si>
+  <si>
+    <t>valid login data with password: "P1@" + "a".repeat(4) (7 characters, meets all rules except minimum length)</t>
+  </si>
+  <si>
+    <t>BVA-2 (pwd=8)</t>
+  </si>
+  <si>
+    <t>valid login data with password: "P1@" + "a".repeat(5) (8 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>success: true, parsed password matches input</t>
+  </si>
+  <si>
+    <t>BVA-3 (pwd=9)</t>
+  </si>
+  <si>
+    <t>valid login data with password: "P1@" + "a".repeat(6) (9 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-4 (pwd=63)</t>
+  </si>
+  <si>
+    <t>valid login data with password: "P1@" + "a".repeat(60) (63 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-5 (pwd=64)</t>
+  </si>
+  <si>
+    <t>valid login data with password: "P1@" + "a".repeat(61) (64 characters, meets all rules)</t>
+  </si>
+  <si>
+    <t>BVA-6 (pwd=65)</t>
+  </si>
+  <si>
+    <t>valid login data with password: "P1@" + "a".repeat(62) (65 characters)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -211,34 +277,25 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid credentials (All fields)</t>
-  </si>
-  <si>
-    <t>Missing email field</t>
-  </si>
-  <si>
-    <t>Missing password field</t>
-  </si>
-  <si>
-    <t>Empty password string</t>
-  </si>
-  <si>
-    <t>Email="invalidemail.com" (Format error)</t>
-  </si>
-  <si>
-    <t>Email with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>password len 0 (Below Min)</t>
-  </si>
-  <si>
-    <t>password len 1 (At Min)</t>
-  </si>
-  <si>
-    <t>password len 2 (Above Min)</t>
+    <t>valid login data with password: "P1@" + "a".repeat(4) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
   </si>
   <si>
     <t>Testing</t>
@@ -271,7 +328,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-01</t>
+    <t>SCHEMA-03</t>
   </si>
   <si>
     <t>n/a</t>
@@ -796,7 +853,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -840,10 +897,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -851,13 +908,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -868,10 +925,10 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -879,13 +936,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -893,13 +950,55 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -909,6 +1008,287 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -922,19 +1302,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -942,16 +1322,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -959,16 +1339,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -976,16 +1356,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -993,16 +1373,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1010,16 +1390,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1027,162 +1407,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1193,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1206,22 +1440,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,19 +1463,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,19 +1483,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1269,19 +1503,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1289,19 +1523,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1309,19 +1543,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1329,19 +1563,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1349,19 +1583,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1369,19 +1603,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,19 +1623,139 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1429,16 +1783,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1446,45 +1800,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B3" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1493,19 +1847,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/loginUserSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/user-schema/loginUserSchema-bbt-form.xlsx
@@ -328,7 +328,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-03</t>
+    <t>SCHEMA-04</t>
   </si>
   <si>
     <t>n/a</t>
